--- a/artfynd/A 54780-2024 artfynd.xlsx
+++ b/artfynd/A 54780-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>363083</v>
+        <v>92580</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601572.5075041824</v>
+        <v>601479</v>
       </c>
       <c r="R2" t="n">
-        <v>7160531.030083683</v>
+        <v>7160327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1566900</v>
+        <v>209049</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601533.852496688</v>
+        <v>601574</v>
       </c>
       <c r="R3" t="n">
-        <v>7160488.418913026</v>
+        <v>7160522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>209049</v>
+        <v>363077</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601573.6701045834</v>
+        <v>601572</v>
       </c>
       <c r="R4" t="n">
-        <v>7160522.030247766</v>
+        <v>7160664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>363084</v>
+        <v>363082</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601467.1004643061</v>
+        <v>601591</v>
       </c>
       <c r="R5" t="n">
-        <v>7160409.574868711</v>
+        <v>7160611</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>363082</v>
+        <v>363083</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601591.3728478329</v>
+        <v>601573</v>
       </c>
       <c r="R6" t="n">
-        <v>7160611.285806757</v>
+        <v>7160531</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>363085</v>
+        <v>363084</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601447.5561785173</v>
+        <v>601467</v>
       </c>
       <c r="R7" t="n">
-        <v>7160362.435985432</v>
+        <v>7160410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,6 +1284,312 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>363085</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Siksjöbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7160362</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>363086</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Siksjöbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601479</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7160327</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1566900</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Siksjöbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7160488</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-09-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
